--- a/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22110" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="SkillConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -35,7 +35,10 @@
     <t>buff执行类型</t>
   </si>
   <si>
-    <t>可变参数</t>
+    <t>Buff持续时间(毫秒)</t>
+  </si>
+  <si>
+    <t>可变Json参数</t>
   </si>
   <si>
     <t>#Note</t>
@@ -44,6 +47,9 @@
     <t>BuffType</t>
   </si>
   <si>
+    <t>DurationTime</t>
+  </si>
+  <si>
     <t>BuffParam</t>
   </si>
   <si>
@@ -56,10 +62,19 @@
     <t>BuffTypeEnum</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>技能可打断前摇-100ms</t>
   </si>
   <si>
-    <t>SingBuff</t>
+    <t>Sing</t>
+  </si>
+  <si>
+    <t>伤害buff</t>
+  </si>
+  <si>
+    <t>Damage</t>
   </si>
 </sst>
 </file>
@@ -1004,15 +1019,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A3:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="5" max="6" width="22.375" customWidth="1"/>
+    <col min="7" max="7" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1022,65 +1037,87 @@
       <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
         <v>10000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:6">
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+    <row r="7" spans="1:7">
+      <c r="C7" s="2">
+        <v>20000</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:6">
-      <c r="F9" s="2"/>
+    <row r="9" spans="1:7">
+      <c r="G9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Id</t>
   </si>
@@ -63,12 +63,6 @@
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>技能可打断前摇-100ms</t>
-  </si>
-  <si>
-    <t>Sing</t>
   </si>
   <si>
     <t>伤害buff</t>
@@ -1019,8 +1013,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A3:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="6" width="22.375" customWidth="1"/>
@@ -1076,48 +1070,31 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
       <c r="C6" s="2">
         <v>10000</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6">
-        <v>100</v>
+      <c r="F6" s="2">
+        <v>0</v>
       </c>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="C7" s="2">
-        <v>20000</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="G9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17175"/>
   </bookViews>
   <sheets>
     <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
@@ -27,29 +27,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+  <si>
+    <t>0 = 不持续执行
+1 = 持续执行 Buff持续时间
+2 = 持续生效 Buff自己退出</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>执行便宜时间</t>
+  </si>
+  <si>
+    <t>持续类型</t>
+  </si>
+  <si>
+    <t>Buff持续时间(毫秒)</t>
+  </si>
+  <si>
     <t>buff执行类型</t>
   </si>
   <si>
-    <t>Buff持续时间(毫秒)</t>
-  </si>
-  <si>
     <t>可变Json参数</t>
   </si>
   <si>
     <t>#Note</t>
   </si>
   <si>
+    <t>OffExecuteTime</t>
+  </si>
+  <si>
+    <t>DurationType</t>
+  </si>
+  <si>
+    <t>DurationTime</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
-    <t>DurationTime</t>
-  </si>
-  <si>
     <t>BuffParam</t>
   </si>
   <si>
@@ -59,16 +76,25 @@
     <t>string</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>BuffTypeEnum</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>伤害buff</t>
+    <t>伤害Buff</t>
   </si>
   <si>
     <t>Damage</t>
+  </si>
+  <si>
+    <t>硬直Buff-1000ms</t>
+  </si>
+  <si>
+    <t>Rigidity</t>
+  </si>
+  <si>
+    <t>{"DurationTime":1000}</t>
   </si>
 </sst>
 </file>
@@ -692,12 +718,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -1013,88 +1045,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A2:I8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="6" width="22.375" customWidth="1"/>
-    <col min="7" max="7" width="19.5" customWidth="1"/>
+    <col min="4" max="5" width="21.625" customWidth="1"/>
+    <col min="6" max="6" width="52.25" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="8" max="8" width="41.75" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="1:7">
+    <row r="2" ht="40.5" spans="6:6">
+      <c r="F2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="3:9">
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="3:9">
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="3:9">
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9">
+      <c r="C6" s="4">
+        <v>10000</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="4">
         <v>0</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4">
+        <v>20001</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
         <v>2</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>3</v>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
-      <c r="C4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="C6" s="2">
-        <v>10000</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="G8" s="2"/>
+    <row r="8" spans="9:9">
+      <c r="I8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
@@ -88,13 +88,13 @@
     <t>Damage</t>
   </si>
   <si>
-    <t>硬直Buff-1000ms</t>
+    <t>硬直Buff-500ms</t>
   </si>
   <si>
     <t>Rigidity</t>
   </si>
   <si>
-    <t>{"DurationTime":1000}</t>
+    <t>{"DurationTime":500}</t>
   </si>
 </sst>
 </file>
@@ -1055,12 +1055,12 @@
     <col min="9" max="9" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="40.5" spans="6:6">
+    <row r="2" ht="40.5" spans="1:9">
       <c r="F2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="3:9">
+    <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:9">
+    <row r="4" s="1" customFormat="1" spans="1:9">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:9">
+    <row r="5" s="1" customFormat="1" spans="1:9">
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="3:9">
+    <row r="6" spans="1:9">
       <c r="C6" s="4">
         <v>10000</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="9:9">
+    <row r="8" spans="1:9">
       <c r="I8" s="4"/>
     </row>
   </sheetData>

--- a/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17175"/>
   </bookViews>
   <sheets>
     <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
@@ -88,13 +88,13 @@
     <t>Damage</t>
   </si>
   <si>
-    <t>硬直Buff-500ms</t>
+    <t>硬直Buff-1000ms</t>
   </si>
   <si>
     <t>Rigidity</t>
   </si>
   <si>
-    <t>{"DurationTime":500}</t>
+    <t>{"DurationTime":1000}</t>
   </si>
 </sst>
 </file>
@@ -1055,12 +1055,12 @@
     <col min="9" max="9" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="40.5" spans="1:9">
+    <row r="2" ht="40.5" spans="6:6">
       <c r="F2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" spans="3:9">
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:9">
+    <row r="4" s="1" customFormat="1" spans="3:9">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:9">
+    <row r="5" s="1" customFormat="1" spans="3:9">
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="3:9">
       <c r="C6" s="4">
         <v>10000</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="9:9">
       <c r="I8" s="4"/>
     </row>
   </sheetData>

--- a/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+  <si>
+    <t xml:space="preserve">1=增益类Buff
+2=减益类Buff
+3=控制类Buff
+4=持续类Buff
+</t>
+  </si>
   <si>
     <t>0 = 不持续执行
 1 = 持续执行 Buff持续时间
@@ -37,7 +44,7 @@
     <t>Id</t>
   </si>
   <si>
-    <t>执行便宜时间</t>
+    <t>执行偏移时间</t>
   </si>
   <si>
     <t>持续类型</t>
@@ -53,6 +60,9 @@
   </si>
   <si>
     <t>#Note</t>
+  </si>
+  <si>
+    <t>Buff类型</t>
   </si>
   <si>
     <t>OffExecuteTime</t>
@@ -718,12 +728,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1045,32 +1058,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:I8"/>
+  <dimension ref="A2:J8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
-    <col min="4" max="5" width="21.625" customWidth="1"/>
-    <col min="6" max="6" width="52.25" customWidth="1"/>
-    <col min="7" max="7" width="22.375" customWidth="1"/>
-    <col min="8" max="8" width="41.75" customWidth="1"/>
-    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="29.875" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="8" width="21.875" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="40.5" spans="6:6">
-      <c r="F2" s="2" t="s">
+    <row r="2" ht="135" customHeight="1" spans="1:10">
+      <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="3:9">
+    <row r="3" s="1" customFormat="1" spans="1:10">
       <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1079,101 +1093,112 @@
       <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:9">
+    <row r="4" s="1" customFormat="1" spans="1:10">
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:9">
+    <row r="5" s="1" customFormat="1" spans="1:10">
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="6" spans="3:9">
-      <c r="C6" s="4">
+    <row r="6" spans="1:10">
+      <c r="C6" s="5">
         <v>10000</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5">
         <v>0</v>
       </c>
-      <c r="F6" s="4">
+      <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4">
+    <row r="7" spans="1:10">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5">
         <v>20001</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5">
         <v>0</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" s="5">
         <v>2</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
+      <c r="I7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="9:9">
-      <c r="I8" s="4"/>
+    <row r="8" spans="1:10">
+      <c r="J8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t xml:space="preserve">1=增益类Buff
 2=减益类Buff
@@ -36,21 +36,10 @@
 </t>
   </si>
   <si>
-    <t>0 = 不持续执行
-1 = 持续执行 Buff持续时间
-2 = 持续生效 Buff自己退出</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
-    <t>执行偏移时间</t>
-  </si>
-  <si>
-    <t>持续类型</t>
-  </si>
-  <si>
-    <t>Buff持续时间(毫秒)</t>
+    <t>Buff类型</t>
   </si>
   <si>
     <t>buff执行类型</t>
@@ -62,19 +51,10 @@
     <t>#Note</t>
   </si>
   <si>
-    <t>Buff类型</t>
-  </si>
-  <si>
-    <t>OffExecuteTime</t>
-  </si>
-  <si>
-    <t>DurationType</t>
-  </si>
-  <si>
-    <t>DurationTime</t>
-  </si>
-  <si>
-    <t>BuffType</t>
+    <t>BuffGroupType</t>
+  </si>
+  <si>
+    <t>BuffHandler</t>
   </si>
   <si>
     <t>BuffParam</t>
@@ -89,7 +69,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>BuffTypeEnum</t>
+    <t>BuffHandlerType</t>
   </si>
   <si>
     <t>伤害Buff</t>
@@ -98,7 +78,7 @@
     <t>Damage</t>
   </si>
   <si>
-    <t>硬直Buff-1000ms</t>
+    <t>硬直状态Buff-1000ms</t>
   </si>
   <si>
     <t>Rigidity</t>
@@ -728,7 +708,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -736,12 +716,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -1058,147 +1032,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:J8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A2:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="29.875" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="8" width="21.875" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="135" customHeight="1" spans="1:10">
+    <row r="2" ht="135" customHeight="1" spans="1:7">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:7">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="1" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
-      <c r="C4" s="1" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="C6" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="F6" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="G6" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
-      <c r="C5" s="1" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3">
+        <v>20001</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="C6" s="5">
-        <v>10000</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5">
-        <v>20001</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="J8" s="5"/>
+    <row r="8" spans="1:7">
+      <c r="G8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/BuffConfig@Buff配置@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t xml:space="preserve">1=增益类Buff
 2=减益类Buff
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>{"DurationTime":1000}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -97,16 +100,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+  <fonts count="20">
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -578,133 +573,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -712,7 +707,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1032,8 +1027,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A2:G11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
@@ -1131,6 +1126,11 @@
     <row r="8" spans="1:7">
       <c r="G8" s="3"/>
     </row>
+    <row r="11" spans="1:7">
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
